--- a/docs/Mapping_casi_uso/matrimoni/Matr_013.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_013.xlsx
@@ -6239,7 +6239,7 @@
         <v>97</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>195</v>
@@ -6354,7 +6354,7 @@
         <v>107</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>195</v>
@@ -6469,7 +6469,7 @@
         <v>117</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>195</v>
@@ -6515,7 +6515,7 @@
         <v>121</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>195</v>
@@ -6538,7 +6538,7 @@
         <v>123</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>195</v>
@@ -6584,7 +6584,7 @@
         <v>127</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>195</v>
@@ -6607,7 +6607,7 @@
         <v>129</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>195</v>
@@ -6630,7 +6630,7 @@
         <v>131</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>195</v>
@@ -6676,7 +6676,7 @@
         <v>135</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>195</v>
@@ -6722,7 +6722,7 @@
         <v>139</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>195</v>
@@ -6768,7 +6768,7 @@
         <v>143</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>195</v>
@@ -6791,7 +6791,7 @@
         <v>145</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>195</v>
@@ -6883,7 +6883,7 @@
         <v>97</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>198</v>
@@ -6998,7 +6998,7 @@
         <v>107</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>198</v>
@@ -7113,7 +7113,7 @@
         <v>117</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>198</v>
@@ -7159,7 +7159,7 @@
         <v>121</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>198</v>
@@ -7182,7 +7182,7 @@
         <v>123</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>198</v>
@@ -7228,7 +7228,7 @@
         <v>127</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>198</v>
@@ -7251,7 +7251,7 @@
         <v>129</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>198</v>
@@ -7274,7 +7274,7 @@
         <v>131</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>198</v>
@@ -7320,7 +7320,7 @@
         <v>135</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>198</v>
@@ -7366,7 +7366,7 @@
         <v>139</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>198</v>
@@ -7412,7 +7412,7 @@
         <v>143</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>198</v>
@@ -7435,7 +7435,7 @@
         <v>145</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>198</v>
